--- a/samples/ss_cirata_ingest.xlsx
+++ b/samples/ss_cirata_ingest.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/samples/ss_cirata_ingest.xlsx
+++ b/samples/ss_cirata_ingest.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U38"/>
+  <dimension ref="A1:U39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 1,2 Cirata 500/150 kV</t>
+          <t>IBT 1 Cirata 500/150 kV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +700,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -738,31 +734,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GITET Cirata 3</t>
+          <t>IBT 2 Cirata 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CRAT37</t>
+          <t>IBT 2 CRATA7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Busbar GITET</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>500 kV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CRATA7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CRATA5</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -774,10 +784,14 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -791,51 +805,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IBT 3 Cirata 500/150 kV</t>
+          <t>GITET Cirata 3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IBT 3 CRAT37</t>
+          <t>CRAT37</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GITET</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>500/150 kV</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CRAT37</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>CRATA5</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
+          <t>500 kV</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>1 IBT (unit 3)</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
@@ -862,35 +858,49 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cirata (bus 150 kV)</t>
+          <t>IBT 3 Cirata 500/150 kV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>IBT 3 CRAT37</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CRAT37</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>CRATA5</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>bus section + kopel</t>
+          <t>1 IBT (unit 3)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -919,17 +929,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PLTA Cirata (Purwakarta)</t>
+          <t>Cirata (bus 150 kV)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KIT_PTUHA</t>
+          <t>CRATA5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -945,7 +955,11 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>bus section + kopel</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
@@ -972,12 +986,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PLTA Jatiluhur</t>
+          <t>PLTA Cirata (Purwakarta)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KIT_JTLHR</t>
+          <t>KIT_PTUHA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1008,14 +1022,10 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1029,12 +1039,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PLTS Cirata</t>
+          <t>PLTA Jatiluhur</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KIT_PLTS</t>
+          <t>KIT_JTLHR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1065,10 +1075,14 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1082,17 +1096,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Purwakarta (Cirata)</t>
+          <t>PLTS Cirata</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PTUHA</t>
+          <t>KIT_PLTS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1135,12 +1149,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jatiluhur</t>
+          <t>Purwakarta (Cirata)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JTLHR</t>
+          <t>PTUHA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1171,14 +1185,10 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1192,12 +1202,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lengkong Dar</t>
+          <t>Jatiluhur</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LGDAR</t>
+          <t>JTLHR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1206,7 +1216,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1218,11 +1228,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>bus section + kopel</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
@@ -1232,10 +1238,14 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1249,12 +1259,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Padalarang Baru</t>
+          <t>Lengkong Dar</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PDLRU</t>
+          <t>LGDAR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1275,7 +1285,11 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>bus section + kopel</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
@@ -1285,14 +1299,10 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1306,12 +1316,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cikampek</t>
+          <t>Padalarang Baru</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CKMPY</t>
+          <t>PDLRU</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1342,10 +1352,14 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1359,12 +1373,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Purwakarta (bus 150 kV)</t>
+          <t>Cikampek</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PWKTA</t>
+          <t>CKMPY</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1395,14 +1409,10 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1416,17 +1426,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV Cirata</t>
+          <t>Purwakarta (bus 150 kV)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IBT 1 CRATA5</t>
+          <t>PWKTA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1434,33 +1444,15 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>CRATA5</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>CRATA4</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>IBT 150/70 kV</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
@@ -1475,7 +1467,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1491,17 +1483,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cirata (bus 70 kV)</t>
+          <t>IBT 150/70 kV Cirata</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CRATA4</t>
+          <t>IBT 1 CRATA5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1509,15 +1501,33 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>CRATA5</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CRATA4</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>IBT 150/70 kV</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
@@ -1548,12 +1558,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bandung Utara</t>
+          <t>Cirata (bus 70 kV)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BDUTR</t>
+          <t>CRATA4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1562,11 +1572,11 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1584,10 +1594,14 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1601,12 +1615,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cibabat Baru</t>
+          <t>Bandung Utara</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CBBRU</t>
+          <t>BDUTR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1637,14 +1651,10 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1658,12 +1668,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cibabat</t>
+          <t>Cibabat Baru</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CBBAT</t>
+          <t>CBBRU</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1694,10 +1704,14 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1711,12 +1725,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Indramayu (bus 150 kV)</t>
+          <t>Cibabat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IDRMA5</t>
+          <t>CBBAT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1764,12 +1778,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pabuaran</t>
+          <t>Indramayu (bus 150 kV)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PBRAN</t>
+          <t>IDRMA5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1817,12 +1831,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Degung Pakar</t>
+          <t>Pabuaran</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DGPKR</t>
+          <t>PBRAN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1831,7 +1845,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1870,51 +1884,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV Purwakarta</t>
+          <t>Degung Pakar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IBT 1 PWKTA</t>
+          <t>DGPKR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>PWKTA</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>PWKTA4</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>2</v>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>IBT 150/70 kV</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
@@ -1941,17 +1937,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Purwakarta (bus 70 kV)</t>
+          <t>IBT 150/70 kV Purwakarta</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PWKTA4</t>
+          <t>IBT 1 PWKTA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1959,15 +1955,33 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>PWKTA</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>PWKTA4</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>IBT 150/70 kV</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
@@ -1994,12 +2008,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Indramayu (bus 70 kV)</t>
+          <t>Purwakarta (bus 70 kV)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IDRMA</t>
+          <t>PWKTA4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2008,7 +2022,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2030,14 +2044,10 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2051,12 +2061,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sipfic</t>
+          <t>Indramayu (bus 70 kV)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SPFIC</t>
+          <t>IDRMA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2092,7 +2102,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2108,12 +2118,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kosambi Baru</t>
+          <t>Sipfic</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>KSBRU</t>
+          <t>SPFIC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2149,7 +2159,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2165,12 +2175,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Subang</t>
+          <t>Kosambi Baru</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SBANG</t>
+          <t>KSBRU</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2206,7 +2216,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2222,12 +2232,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Indocement</t>
+          <t>Subang</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>INDCI</t>
+          <t>SBANG</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2236,7 +2246,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2258,10 +2268,14 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2275,12 +2289,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cigunea</t>
+          <t>Indocement</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CGNEA</t>
+          <t>INDCI</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2328,12 +2342,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Indramayu Barat</t>
+          <t>Cigunea</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IDBRT</t>
+          <t>CGNEA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2381,12 +2395,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Curug</t>
+          <t>Indramayu Barat</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CURUG</t>
+          <t>IDBRT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2434,12 +2448,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tegal Tanjung Baru (SS Cibatu 3,4)</t>
+          <t>Curug</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TTJBR</t>
+          <t>CURUG</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2448,11 +2462,11 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -2460,22 +2474,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>batas ke Subsistem Cibatu 3,4</t>
-        </is>
-      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -2495,12 +2501,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pondok Ali (SS Cibatu 3,4)</t>
+          <t>Tegal Tanjung Baru (SS Cibatu 3,4)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PNDLI</t>
+          <t>TTJBR</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2509,11 +2515,11 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -2556,12 +2562,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rendeh Salak (SS Cibatu 3,4)</t>
+          <t>Pondok Ali (SS Cibatu 3,4)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RDSLK</t>
+          <t>PNDLI</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2617,12 +2623,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cigereleng (SS Bandung Selatan)</t>
+          <t>Rendeh Salak (SS Cibatu 3,4)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CGRLG</t>
+          <t>RDSLK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2631,11 +2637,11 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -2645,7 +2651,7 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Bandung Selatan 1,2 - New Ujungberung 1,2</t>
+          <t>batas ke Subsistem Cibatu 3,4</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -2678,12 +2684,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ujung Berung (SS Bandung Selatan)</t>
+          <t>Cigereleng (SS Bandung Selatan)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UBRNG</t>
+          <t>CGRLG</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2692,7 +2698,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2732,6 +2738,67 @@
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Ujung Berung (SS Bandung Selatan)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>UBRNG</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>batas ke Subsistem Bandung Selatan 1,2 - New Ujungberung 1,2</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4639,12 +4706,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[N-1] 1. Pembebanan IBT 1, 2 &amp; 3 GITET Cirata sudah di atas 60% (IBT-1,2 @77%, IBT-3 82%) kondisi operasi parallel 3 IBT, looping jauh 3 IBT 500/150 kV GITET Cirata di Penghantar SUTT 150 kV Cirata - Cikumpay - Purwakarta. 2. Besarnya Short Circuit Level (&gt;40 kA) di GI 150 kV Cirata apabila seluruh unit PLTA Cirata, PLTA Saguling, dan minimal 2 unit PLTA Jatiluhur dioperasikan di SS Cirata 1,2,3</t>
+          <t>[BELUM_DITETAPKAN] 1. Pembebanan IBT 1, 2 &amp; 3 GITET Cirata sudah di atas 60% (IBT-1,2 @77%, IBT-3 82%) kondisi operasi parallel 3 IBT, looping jauh 3 IBT 500/150 kV GITET Cirata di Penghantar SUTT 150 kV Cirata - Cikumpay - Purwakarta. 2. Besarnya Short Circuit Level (&gt;40 kA) di GI 150 kV Cirata apabila seluruh unit PLTA Cirata, PLTA Saguling, dan minimal 2 unit PLTA Jatiluhur dioperasikan di SS Cirata 1,2,3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4674,12 +4741,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[N-1] Bottleneck pada MTU (Inom=800A) dan tidak ada kopel di GI 150 kV Jatiluhur karena terkendala asset milik PLTA Jatiluhur sehingga mengurangi keandalan dan fleksibilitas pengoperasian Subsistem Cirata dan Subsistem Cibatu 3,4-Mandirancan 1,2. Sedangkan ruas Tatajabar-Jatiluhur dan Padalarang-Jatiluhur sudah diuprating (Inom=1584 A)</t>
+          <t>[BELUM_DITETAPKAN] Bottleneck pada MTU (Inom=800A) dan tidak ada kopel di GI 150 kV Jatiluhur karena terkendala asset milik PLTA Jatiluhur sehingga mengurangi keandalan dan fleksibilitas pengoperasian Subsistem Cirata dan Subsistem Cibatu 3,4-Mandirancan 1,2. Sedangkan ruas Tatajabar-Jatiluhur dan Padalarang-Jatiluhur sudah diuprating (Inom=1584 A)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4709,12 +4776,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Cirata-Padalarang 1,2 diatas 70% (@79%) karena bottleneck dengan kapasitas terpasang 1200 A sepanjang 27,10 km (sisi Padalarang) &amp; 1620 A sepanjang 10 km (sisi Cirata)</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan SUTT 150 kV Cirata-Padalarang 1,2 diatas 70% (@79%) karena bottleneck dengan kapasitas terpasang 1200 A sepanjang 27,10 km (sisi Padalarang) &amp; 1620 A sepanjang 10 km (sisi Cirata)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4954,12 +5021,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[N-1] Terdapat Bottleneck pada pola operasi busbar 70 kV GI Kosambi Baru karena adanya perbedaan rasio tegangan antara IBT 150/66 Kosambi Baru 1,4 dengan IBT150/70 kV Purwakarta 1,2</t>
+          <t>[BELUM_DITETAPKAN] Terdapat Bottleneck pada pola operasi busbar 70 kV GI Kosambi Baru karena adanya perbedaan rasio tegangan antara IBT 150/66 Kosambi Baru 1,4 dengan IBT150/70 kV Purwakarta 1,2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">

--- a/samples/ss_cirata_ingest.xlsx
+++ b/samples/ss_cirata_ingest.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gardu_Induk_dan_Aset" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jalur_Transmisi" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Kerawanan_Detail" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bay" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Kerawanan_Detail" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4655,6 +4656,272 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Kode GI</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nama GI</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Feeder (GI Induk)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Jenis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Tegangan</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Jumlah Sirkit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Status Operasi</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>No Kerawanan</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Sudut Pandang</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CGRLG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Cigereleng</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LGDAR</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PNDLI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Pondok Ali</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>KSBRU</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RDSLK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Rendeh Salak (SS Cibatu 3,4)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>KSBRU</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TTJBR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tegal Tanjung Baru</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>JTLHR</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>UBRNG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ujung Berung</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DGPKR</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
